--- a/ShortStrangle_Dashboard.xlsx
+++ b/ShortStrangle_Dashboard.xlsx
@@ -7,10 +7,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tab1_Backtest" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tab2_LiveSignal" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tab3_IV_History" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase2_Roadmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tab1_Backtest" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tab2_LiveSignal" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tab3_IV_History" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -26,7 +27,7 @@
     <numFmt numFmtId="167" formatCode="0&quot;/100&quot;"/>
     <numFmt numFmtId="168" formatCode="\₹#,##0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -133,8 +134,16 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
+    </font>
   </fonts>
-  <fills count="20">
+  <fills count="25">
     <fill>
       <patternFill/>
     </fill>
@@ -249,6 +258,36 @@
         <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E24B4A"/>
+        <bgColor rgb="00E24B4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0070AD47"/>
+        <bgColor rgb="0070AD47"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0092D050"/>
+        <bgColor rgb="0092D050"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -355,7 +394,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -565,6 +604,16 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -824,7 +873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1423,6 +1472,80 @@
       <c r="C22" s="70" t="inlineStr">
         <is>
           <t>Phase 4 (Tab 3 labels + Changelog); NSE margin data integration; Historical data validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="64" t="inlineStr">
+        <is>
+          <t>Phase 2</t>
+        </is>
+      </c>
+      <c r="B24" s="64" t="inlineStr">
+        <is>
+          <t>Historical Premium Cache</t>
+        </is>
+      </c>
+      <c r="C24" s="67" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="D24" s="64" t="inlineStr">
+        <is>
+          <t>Add Google Sheets/SQLite caching for option premiums; Build scheduled update job</t>
+        </is>
+      </c>
+      <c r="E24" s="64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F24" s="64" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G24" s="64" t="inlineStr">
+        <is>
+          <t>Enables accurate backtesting without repeated API calls; Required for Tab 4 validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="64" t="inlineStr">
+        <is>
+          <t>Phase 2</t>
+        </is>
+      </c>
+      <c r="B26" s="64" t="inlineStr">
+        <is>
+          <t>Historical Premium Cache</t>
+        </is>
+      </c>
+      <c r="C26" s="67" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="D26" s="64" t="inlineStr">
+        <is>
+          <t>Add Google Sheets/SQLite caching for option premiums; Build scheduled update job</t>
+        </is>
+      </c>
+      <c r="E26" s="64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F26" s="64" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G26" s="64" t="inlineStr">
+        <is>
+          <t>Enables accurate backtesting without repeated API calls; Required for Tab 4 validation</t>
         </is>
       </c>
     </row>
@@ -1442,6 +1565,229 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25" customHeight="1">
+      <c r="A1" s="73" t="inlineStr">
+        <is>
+          <t>Phase 2 Roadmap: Historical Data Caching Strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="74" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="64" t="inlineStr">
+        <is>
+          <t>Current implementation fetches option premiums from Kite API on every page load (Tab 2 live signal). Tab 1 backtest uses formula-based premium estimation instead of historical actual premiums. This approach has limitations:
+• Repeated API calls = rate limiting + latency
+• No historical premium archive = backtests inaccurate
+• Cannot validate strategy offline</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="75" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="64" t="inlineStr">
+        <is>
+          <t>Build a historical premium cache (Google Sheets or SQLite database) that stores:
+• Date, Time, Instrument, Strike, Expiry, Premium (CE), Premium (PE), IV, IVP
+• Updated weekly after expiry via separate scheduled job
+• Queried by backtest module to validate P&amp;L assumptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="76" t="inlineStr">
+        <is>
+          <t>Implementation Steps</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="50" customHeight="1">
+      <c r="A10" s="77" t="inlineStr">
+        <is>
+          <t>Step 1: Google Sheets Setup</t>
+        </is>
+      </c>
+      <c r="B10" s="64" t="inlineStr">
+        <is>
+          <t>Create "NIFTY_Premium_History" and "SENSEX_Premium_History" sheets in shared Google Drive. Each row: Date | Time | Strike | Expiry | IV | IVP | CE_Premium | PE_Premium | Notes. Share via gspread (Python library).</t>
+        </is>
+      </c>
+      <c r="C10" s="78" t="inlineStr">
+        <is>
+          <t>Week 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="50" customHeight="1">
+      <c r="A11" s="77" t="inlineStr">
+        <is>
+          <t>Step 2: Historical Data Backfill</t>
+        </is>
+      </c>
+      <c r="B11" s="64" t="inlineStr">
+        <is>
+          <t>Fetch last 12 weeks of NSE Bhavcopy option data via yfinance or nsepy. Parse CSV, extract premiums for ±2.5%/±3%/±3.5%/±4%/±4.5% strikes. Populate Google Sheets (1,000-1,500 rows per instrument).</t>
+        </is>
+      </c>
+      <c r="C11" s="78" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="50" customHeight="1">
+      <c r="A12" s="77" t="inlineStr">
+        <is>
+          <t>Step 3: Scheduled Update Job</t>
+        </is>
+      </c>
+      <c r="B12" s="64" t="inlineStr">
+        <is>
+          <t>Create daily cron job (Cloud Functions or local scheduler) that:
+  a) Runs after NSE market close
+  b) Fetches today's option premiums from Kite API
+  c) Appends to Google Sheets
+  d) Updates IVP calculation
+Keep 52-week rolling window (delete rows older than 1 year).</t>
+        </is>
+      </c>
+      <c r="C12" s="78" t="inlineStr">
+        <is>
+          <t>Week 2-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="77" t="inlineStr">
+        <is>
+          <t>Step 4: Backtest Integration</t>
+        </is>
+      </c>
+      <c r="B13" s="64" t="inlineStr">
+        <is>
+          <t>Update generate_backtest_pnl():
+  a) Query Google Sheets for date range matching lookback_m
+  b) For each offset, fetch mean/median premium from cache
+  c) Calculate win_rate and loss_per_trade from actual trade history
+  d) Compare formula-based P&amp;L vs. actual historical P&amp;L</t>
+        </is>
+      </c>
+      <c r="C13" s="78" t="inlineStr">
+        <is>
+          <t>Week 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="50" customHeight="1">
+      <c r="A14" s="77" t="inlineStr">
+        <is>
+          <t>Step 5: Validation &amp; Dashboard</t>
+        </is>
+      </c>
+      <c r="B14" s="64" t="inlineStr">
+        <is>
+          <t>Add new Tab 4: "Historical Validation" showing:
+  - Backtest P&amp;L (formula-based) vs. Actual Historical P&amp;L (from cache)
+  - Win rate distribution by IV regime (LOW/MID/HIGH)
+  - Best performing offset + IV combination
+  - Confidence level: "High (12+ weeks data)" or "Low (&lt; 4 weeks)"</t>
+        </is>
+      </c>
+      <c r="C14" s="78" t="inlineStr">
+        <is>
+          <t>Week 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="79" t="inlineStr">
+        <is>
+          <t>Dependencies &amp; Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="80" t="inlineStr">
+        <is>
+          <t>Google Sheets API + gspread (Python)</t>
+        </is>
+      </c>
+      <c r="B17" s="64" t="inlineStr">
+        <is>
+          <t>pip install gspread google-auth-oauthlib. Alternative: SQLite for local DB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="80" t="inlineStr">
+        <is>
+          <t>NSE Bhavcopy fetch</t>
+        </is>
+      </c>
+      <c r="B18" s="64" t="inlineStr">
+        <is>
+          <t>yfinance or nsepy library. Alternative: Manual CSV download from NSE website.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="80" t="inlineStr">
+        <is>
+          <t>Cloud scheduler (optional)</t>
+        </is>
+      </c>
+      <c r="B19" s="64" t="inlineStr">
+        <is>
+          <t>Google Cloud Functions (free tier: 2M invocations/month). Alternative: Local cron job on always-on machine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="80" t="inlineStr">
+        <is>
+          <t>Kite Connect API</t>
+        </is>
+      </c>
+      <c r="B20" s="64" t="inlineStr">
+        <is>
+          <t>Already integrated. Continue using for live quotes + daily scheduled updates.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
@@ -1821,7 +2167,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2842,7 +3188,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3656,7 +4002,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
